--- a/FL-corrections-structure/ig/StructureDefinition-fr-core-slot.xlsx
+++ b/FL-corrections-structure/ig/StructureDefinition-fr-core-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-08T19:18:35+00:00</t>
+    <t>2026-03-11T17:39:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -846,7 +846,7 @@
     <t>The style of appointment or patient that may be booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0276|3.0.0</t>
   </si>
   <si>
     <t>Slot.schedule</t>
